--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef2a052af30ca56b/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D91B9DD2-5260-4438-A88C-AD0A7FF0D9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{CE1D4048-F040-4A3C-B9C6-4050C958A65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3555" windowWidth="29040" windowHeight="15720" xr2:uid="{3E7A277E-4E3E-4986-9C96-0150DB9E36CA}"/>
+    <workbookView xWindow="28680" yWindow="-2670" windowWidth="29040" windowHeight="15720" xr2:uid="{3E7A277E-4E3E-4986-9C96-0150DB9E36CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Product</t>
   </si>
@@ -51,9 +47,6 @@
   </si>
   <si>
     <t>Borosil bottle</t>
-  </si>
-  <si>
-    <t>Beco tissue</t>
   </si>
 </sst>
 </file>
@@ -456,11 +449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
